--- a/inst/extdata/ex03/User_05032018.xlsx
+++ b/inst/extdata/ex03/User_05032018.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Blank" sheetId="3" r:id="rId1"/>
@@ -49,12 +49,6 @@
     <t>BLANK</t>
   </si>
   <si>
-    <t>SN1</t>
-  </si>
-  <si>
-    <t>SN2</t>
-  </si>
-  <si>
     <t>Sample</t>
   </si>
   <si>
@@ -89,9 +83,6 @@
   </si>
   <si>
     <t>Concentration (µg/L)</t>
-  </si>
-  <si>
-    <t>LYSAT</t>
   </si>
   <si>
     <t>Target</t>
@@ -134,6 +125,15 @@
   </si>
   <si>
     <t>siGENE_AB</t>
+  </si>
+  <si>
+    <t>LYSATE</t>
+  </si>
+  <si>
+    <t>SUPERNATANT1</t>
+  </si>
+  <si>
+    <t>SUPERNATANT2</t>
   </si>
 </sst>
 </file>
@@ -2924,13 +2924,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -2939,19 +2939,19 @@
         <v>0</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -2959,10 +2959,10 @@
         <v>43164</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -3213,22 +3213,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -3237,19 +3237,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -3266,20 +3266,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f t="shared" ref="D2:D19" ca="1" si="0">RIGHT(CELL("nomfichier",A1),LEN(CELL("nomfichier",A1))-SEARCH("]",CELL("nomfichier",A1)))</f>
+        <f ca="1">RIGHT(CELL("nomfichier",A1),LEN(CELL("nomfichier",A1))-SEARCH("]",CELL("nomfichier",A1)))</f>
         <v>siNTP</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>0.65627120000000005</v>
@@ -3299,7 +3299,7 @@
         <v>1479.4059007533888</v>
       </c>
       <c r="N2" s="1">
-        <f t="shared" ref="N2:N19" si="1">(L2/10^3 * M2)</f>
+        <f t="shared" ref="N2:N19" si="0">(L2/10^3 * M2)</f>
         <v>73.970295037669445</v>
       </c>
       <c r="O2" s="1"/>
@@ -3318,20 +3318,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ref="D3:D19" ca="1" si="1">RIGHT(CELL("nomfichier",A2),LEN(CELL("nomfichier",A2))-SEARCH("]",CELL("nomfichier",A2)))</f>
         <v>siNTP</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.70412640000000004</v>
@@ -3351,7 +3351,7 @@
         <v>1515.2849726701259</v>
       </c>
       <c r="N3" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>75.764248633506298</v>
       </c>
       <c r="O3" s="1"/>
@@ -3370,20 +3370,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D4" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.64966840000000003</v>
@@ -3403,7 +3403,7 @@
         <v>1409.7128809221244</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>70.485644046106231</v>
       </c>
       <c r="O4" s="1"/>
@@ -3422,20 +3422,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I5" s="1">
         <v>0.63302199999999997</v>
@@ -3455,7 +3455,7 @@
         <v>1361.8540018003491</v>
       </c>
       <c r="N5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>68.092700090017459</v>
       </c>
       <c r="O5" s="1"/>
@@ -3474,20 +3474,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I6" s="1">
         <v>0.61521700000000001</v>
@@ -3507,7 +3507,7 @@
         <v>1290.9028095422809</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>64.545140477114046</v>
       </c>
       <c r="O6" s="1"/>
@@ -3526,20 +3526,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D7" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I7" s="1">
         <v>0.62787649999999995</v>
@@ -3559,7 +3559,7 @@
         <v>1314.5850608530984</v>
       </c>
       <c r="N7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>65.729253042654918</v>
       </c>
       <c r="O7" s="1"/>
@@ -3577,21 +3577,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D8" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D8" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
         <v>26</v>
       </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.23576630000000001</v>
@@ -3610,7 +3610,7 @@
         <v>6.0618585793661008</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.60618585793661017</v>
       </c>
       <c r="O8">
@@ -3631,21 +3631,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D9" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D9" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
         <v>26</v>
       </c>
-      <c r="G9" t="s">
-        <v>29</v>
-      </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.24887029999999999</v>
@@ -3664,7 +3664,7 @@
         <v>6.3753465157495901</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.63753465157495903</v>
       </c>
       <c r="O9">
@@ -3685,21 +3685,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D10" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D10" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
         <v>26</v>
       </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.2459665</v>
@@ -3718,7 +3718,7 @@
         <v>6.1152573634473155</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.61152573634473162</v>
       </c>
       <c r="O10">
@@ -3739,21 +3739,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D11" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D11" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I11">
         <v>0.38160729999999998</v>
@@ -3772,7 +3772,7 @@
         <v>19.983572832695753</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.9983572832695753</v>
       </c>
       <c r="O11">
@@ -3793,21 +3793,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D12" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D12" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I12">
         <v>0.37907980000000002</v>
@@ -3826,7 +3826,7 @@
         <v>19.91206323372753</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.9912063233727531</v>
       </c>
       <c r="O12">
@@ -3847,21 +3847,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D13" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D13" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I13">
         <v>0.3732723</v>
@@ -3880,7 +3880,7 @@
         <v>19.605612291859906</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.9605612291859906</v>
       </c>
       <c r="O13">
@@ -3902,20 +3902,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D14" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.50897029999999999</v>
@@ -3934,7 +3934,7 @@
         <v>32.228443612487268</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.2228443612487272</v>
       </c>
       <c r="O14" s="1">
@@ -3956,20 +3956,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D15" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.48153639999999998</v>
@@ -3988,7 +3988,7 @@
         <v>29.959158701405745</v>
       </c>
       <c r="N15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.9959158701405748</v>
       </c>
       <c r="O15" s="1">
@@ -4010,20 +4010,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D16" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.55124209999999996</v>
@@ -4042,7 +4042,7 @@
         <v>33.724483868245521</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3724483868245523</v>
       </c>
       <c r="O16" s="1">
@@ -4064,20 +4064,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D17" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I17" s="1">
         <v>0.73388200000000003</v>
@@ -4096,7 +4096,7 @@
         <v>54.255302682635701</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.4255302682635707</v>
       </c>
       <c r="O17" s="1">
@@ -4118,20 +4118,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D18" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I18" s="1">
         <v>1.048583</v>
@@ -4150,7 +4150,7 @@
         <v>80.003108600166399</v>
       </c>
       <c r="N18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8.0003108600166399</v>
       </c>
       <c r="O18" s="1">
@@ -4172,20 +4172,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D19" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siNTP</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I19" s="1">
         <v>0.8531126</v>
@@ -4204,7 +4204,7 @@
         <v>62.086257815073125</v>
       </c>
       <c r="N19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.2086257815073127</v>
       </c>
       <c r="O19" s="1">
@@ -4244,22 +4244,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -4268,19 +4268,19 @@
         <v>0</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -4297,20 +4297,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f t="shared" ref="D2:D19" ca="1" si="0">RIGHT(CELL("nomfichier",A7),LEN(CELL("nomfichier",A7))-SEARCH("]",CELL("nomfichier",A7)))</f>
+        <f ca="1">RIGHT(CELL("nomfichier",A1),LEN(CELL("nomfichier",A1))-SEARCH("]",CELL("nomfichier",A1)))</f>
         <v>siGENE</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>0.64171560000000005</v>
@@ -4330,7 +4330,7 @@
         <v>1462.2221656672075</v>
       </c>
       <c r="N2" s="1">
-        <f t="shared" ref="N2:N19" si="1">(L2/10^3 * M2)</f>
+        <f t="shared" ref="N2:N19" si="0">(L2/10^3 * M2)</f>
         <v>73.11110828336038</v>
       </c>
       <c r="O2" s="1"/>
@@ -4349,20 +4349,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ref="D3:D19" ca="1" si="1">RIGHT(CELL("nomfichier",A2),LEN(CELL("nomfichier",A2))-SEARCH("]",CELL("nomfichier",A2)))</f>
         <v>siGENE</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>0.61800370000000004</v>
@@ -4382,7 +4382,7 @@
         <v>1331.8913401791262</v>
       </c>
       <c r="N3" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>66.594567008956318</v>
       </c>
       <c r="O3" s="1"/>
@@ -4401,20 +4401,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D4" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>0.65488559999999996</v>
@@ -4434,7 +4434,7 @@
         <v>1431.7222078163061</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>71.586110390815307</v>
       </c>
       <c r="O4" s="1"/>
@@ -4453,20 +4453,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I5" s="1">
         <v>0.55879939999999995</v>
@@ -4486,7 +4486,7 @@
         <v>1201.8389634363507</v>
       </c>
       <c r="N5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>60.091948171817535</v>
       </c>
       <c r="O5" s="1"/>
@@ -4505,20 +4505,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I6" s="1">
         <v>0.58267420000000003</v>
@@ -4538,7 +4538,7 @@
         <v>1193.6012289862181</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>59.680061449310905</v>
       </c>
       <c r="O6" s="1"/>
@@ -4557,20 +4557,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D7" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I7" s="1">
         <v>0.60214330000000005</v>
@@ -4590,7 +4590,7 @@
         <v>1263.5672212661409</v>
       </c>
       <c r="N7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>63.178361063307051</v>
       </c>
       <c r="O7" s="1"/>
@@ -4608,21 +4608,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D8" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D8" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>0.27633999999999997</v>
@@ -4641,7 +4641,7 @@
         <v>10.112651726628847</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.0112651726628847</v>
       </c>
       <c r="O8">
@@ -4662,21 +4662,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D9" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D9" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>0.26498090000000002</v>
@@ -4695,7 +4695,7 @@
         <v>8.2055273947945082</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.82055273947945084</v>
       </c>
       <c r="O9">
@@ -4716,21 +4716,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D10" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D10" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>0.27241500000000002</v>
@@ -4749,7 +4749,7 @@
         <v>9.0480198177226061</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.90480198177226068</v>
       </c>
       <c r="O10">
@@ -4770,21 +4770,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D11" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D11" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I11">
         <v>0.33661829999999998</v>
@@ -4803,7 +4803,7 @@
         <v>17.053579084189369</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.705357908418937</v>
       </c>
       <c r="O11">
@@ -4824,21 +4824,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D12" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D12" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I12">
         <v>0.31245509999999999</v>
@@ -4857,7 +4857,7 @@
         <v>13.306310034079095</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.3306310034079096</v>
       </c>
       <c r="O12">
@@ -4878,21 +4878,21 @@
         <f>Blank!C$2</f>
         <v>siGENE_AB</v>
       </c>
-      <c r="D13" s="4" t="str">
-        <f t="shared" ca="1" si="0"/>
+      <c r="D13" s="5" t="str">
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I13">
         <v>0.27813660000000001</v>
@@ -4911,7 +4911,7 @@
         <v>8.9433258366535942</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8943325836653595</v>
       </c>
       <c r="O13">
@@ -4933,20 +4933,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D14" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1">
         <v>0.41087089999999998</v>
@@ -4965,7 +4965,7 @@
         <v>23.237787833759501</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.3237787833759502</v>
       </c>
       <c r="O14" s="1">
@@ -4987,20 +4987,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D15" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="1">
         <v>0.35466619999999999</v>
@@ -5019,7 +5019,7 @@
         <v>16.702048645089526</v>
       </c>
       <c r="N15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.6702048645089527</v>
       </c>
       <c r="O15" s="1">
@@ -5041,20 +5041,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D16" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1">
         <v>0.43496220000000002</v>
@@ -5073,7 +5073,7 @@
         <v>24.546276209403501</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.4546276209403501</v>
       </c>
       <c r="O16" s="1">
@@ -5095,20 +5095,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D17" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I17" s="1">
         <v>0.90000599999999997</v>
@@ -5127,7 +5127,7 @@
         <v>65.53584557725442</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.5535845577254426</v>
       </c>
       <c r="O17" s="1">
@@ -5149,20 +5149,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D18" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I18" s="1">
         <v>0.93077980000000005</v>
@@ -5181,7 +5181,7 @@
         <v>66.733179593608384</v>
       </c>
       <c r="N18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.6733179593608387</v>
       </c>
       <c r="O18" s="1">
@@ -5203,20 +5203,20 @@
         <v>siGENE_AB</v>
       </c>
       <c r="D19" s="1" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>siGENE</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I19" s="1">
         <v>0.77950129999999995</v>
@@ -5235,7 +5235,7 @@
         <v>56.763222184954635</v>
       </c>
       <c r="N19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.6763222184954643</v>
       </c>
       <c r="O19" s="1">
